--- a/dados/excel/indice.xlsx
+++ b/dados/excel/indice.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Índice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Índice'!$A$4:$F$52</definedName>
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 10/10/2026 14:55 · 48 arquivos com sucesso</t>
+          <t>Gerado em 12/10/2026 16:30 · 48 arquivos com sucesso</t>
         </is>
       </c>
     </row>

--- a/dados/excel/indice.xlsx
+++ b/dados/excel/indice.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 12/10/2026 16:30 · 48 arquivos com sucesso</t>
+          <t>Gerado em 16/10/2026 19:58 · 48 arquivos com sucesso</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>9</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>4</v>
